--- a/lang/lt/headTags.xlsx
+++ b/lang/lt/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1194</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1198</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2129">
   <si>
     <t>en</t>
   </si>
@@ -5152,6 +5152,18 @@
     <t>Shulker</t>
   </si>
   <si>
+    <t>Sift (Inspired)</t>
+  </si>
+  <si>
+    <t>„Sift“ (įkvėpta)</t>
+  </si>
+  <si>
+    <t>Sift (Vanilla)</t>
+  </si>
+  <si>
+    <t>„Sift“ (vanilė)</t>
+  </si>
+  <si>
     <t>Silent Hill</t>
   </si>
   <si>
@@ -5977,6 +5989,12 @@
     <t>ULTRAKILL</t>
   </si>
   <si>
+    <t>Umamusume</t>
+  </si>
+  <si>
+    <t>„Umamusume“</t>
+  </si>
+  <si>
     <t>Umineko - When They Cry</t>
   </si>
   <si>
@@ -6245,6 +6263,12 @@
   </si>
   <si>
     <t>Žiema</t>
+  </si>
+  <si>
+    <t>Winter Drop</t>
+  </si>
+  <si>
+    <t>Žiemos kolekcija</t>
   </si>
   <si>
     <t>Witcher</t>
@@ -6726,7 +6750,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1194"/>
+  <dimension ref="A1:B1198"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14434,28 +14458,28 @@
         <v>1711</v>
       </c>
       <c r="B963" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B964" t="s">
-        <v>1712</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1713</v>
+        <v>1715</v>
       </c>
       <c r="B965" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B966" t="s">
         <v>1716</v>
@@ -14490,28 +14514,28 @@
         <v>1723</v>
       </c>
       <c r="B970" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="B971" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
       <c r="B972" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="B973" t="s">
         <v>1728</v>
@@ -14562,28 +14586,28 @@
         <v>1739</v>
       </c>
       <c r="B979" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="B980" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="B981" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="B982" t="s">
         <v>1744</v>
@@ -14674,28 +14698,28 @@
         <v>1765</v>
       </c>
       <c r="B993" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="B994" t="s">
-        <v>1766</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1767</v>
+        <v>1769</v>
       </c>
       <c r="B995" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B996" t="s">
         <v>1770</v>
@@ -14722,55 +14746,55 @@
         <v>1775</v>
       </c>
       <c r="B999" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="B1000" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="B1001" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="B1002" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="B1003" t="s">
-        <v>1780</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="B1004" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B1005" t="s">
         <v>1784</v>
-      </c>
-      <c r="B1005" t="s">
-        <v>1785</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
@@ -14786,20 +14810,20 @@
         <v>1788</v>
       </c>
       <c r="B1007" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="B1008" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="B1009" t="s">
         <v>1792</v>
@@ -14810,20 +14834,20 @@
         <v>1793</v>
       </c>
       <c r="B1010" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="B1011" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B1012" t="s">
         <v>1797</v>
@@ -14874,28 +14898,28 @@
         <v>1808</v>
       </c>
       <c r="B1018" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B1019" t="s">
-        <v>1809</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1810</v>
+        <v>1812</v>
       </c>
       <c r="B1020" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="B1021" t="s">
         <v>1813</v>
@@ -14906,44 +14930,44 @@
         <v>1814</v>
       </c>
       <c r="B1022" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B1023" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="B1024" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B1025" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="B1026" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="B1027" t="s">
         <v>1822</v>
@@ -14970,28 +14994,28 @@
         <v>1827</v>
       </c>
       <c r="B1030" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B1031" t="s">
-        <v>1828</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1829</v>
+        <v>1831</v>
       </c>
       <c r="B1032" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="B1033" t="s">
         <v>1832</v>
@@ -15002,20 +15026,20 @@
         <v>1833</v>
       </c>
       <c r="B1034" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B1035" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B1036" t="s">
         <v>1837</v>
@@ -15058,20 +15082,20 @@
         <v>1846</v>
       </c>
       <c r="B1041" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="B1042" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="B1043" t="s">
         <v>1850</v>
@@ -15098,36 +15122,36 @@
         <v>1855</v>
       </c>
       <c r="B1046" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B1047" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B1048" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="B1049" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="B1050" t="s">
         <v>1862</v>
@@ -15138,20 +15162,20 @@
         <v>1863</v>
       </c>
       <c r="B1051" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="B1052" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="B1053" t="s">
         <v>1867</v>
@@ -15170,20 +15194,20 @@
         <v>1870</v>
       </c>
       <c r="B1055" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="B1056" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="B1057" t="s">
         <v>1874</v>
@@ -15322,20 +15346,20 @@
         <v>1907</v>
       </c>
       <c r="B1074" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="B1075" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="B1076" t="s">
         <v>1911</v>
@@ -15402,20 +15426,20 @@
         <v>1926</v>
       </c>
       <c r="B1084" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="B1085" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="B1086" t="s">
         <v>1930</v>
@@ -15426,52 +15450,52 @@
         <v>1931</v>
       </c>
       <c r="B1087" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="B1088" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="B1089" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="B1090" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="B1091" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="B1092" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="B1093" t="s">
         <v>1941</v>
@@ -15482,20 +15506,20 @@
         <v>1942</v>
       </c>
       <c r="B1094" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="B1095" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="B1096" t="s">
         <v>1946</v>
@@ -15506,20 +15530,20 @@
         <v>1947</v>
       </c>
       <c r="B1097" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="B1098" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="B1099" t="s">
         <v>1951</v>
@@ -15586,20 +15610,20 @@
         <v>1966</v>
       </c>
       <c r="B1107" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="B1108" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="B1109" t="s">
         <v>1970</v>
@@ -15666,52 +15690,52 @@
         <v>1985</v>
       </c>
       <c r="B1117" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="B1118" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="B1119" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="B1120" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="B1121" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="B1122" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="B1123" t="s">
         <v>1995</v>
@@ -15730,44 +15754,44 @@
         <v>1998</v>
       </c>
       <c r="B1125" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B1126" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B1127" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="B1128" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B1129" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B1130" t="s">
         <v>2007</v>
@@ -15906,100 +15930,100 @@
         <v>2040</v>
       </c>
       <c r="B1147" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="B1148" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="B1149" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="B1150" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="B1151" t="s">
-        <v>2046</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="B1152" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="B1153" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="B1154" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="B1155" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="B1156" t="s">
-        <v>2053</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>2054</v>
+        <v>2057</v>
       </c>
       <c r="B1157" t="s">
-        <v>2055</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="B1158" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="B1159" t="s">
         <v>2059</v>
@@ -16074,36 +16098,36 @@
         <v>2076</v>
       </c>
       <c r="B1168" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="B1169" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="B1170" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="B1171" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="B1172" t="s">
         <v>2084</v>
@@ -16122,44 +16146,44 @@
         <v>2087</v>
       </c>
       <c r="B1174" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="B1175" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>2089</v>
+        <v>2091</v>
       </c>
       <c r="B1176" t="s">
-        <v>2090</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>2091</v>
+        <v>2093</v>
       </c>
       <c r="B1177" t="s">
-        <v>2092</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="B1178" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="B1179" t="s">
         <v>2096</v>
@@ -16170,123 +16194,155 @@
         <v>2097</v>
       </c>
       <c r="B1180" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="B1181" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="B1182" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="B1183" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="B1184" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="B1185" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="B1186" t="s">
-        <v>2106</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>2107</v>
+        <v>2110</v>
       </c>
       <c r="B1187" t="s">
-        <v>2108</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>2109</v>
+        <v>2112</v>
       </c>
       <c r="B1188" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="B1189" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="B1190" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="B1191" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="B1192" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="B1193" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="B1194" t="s">
-        <v>2120</v>
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:2">
+      <c r="A1195" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B1195" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:2">
+      <c r="A1196" t="s">
+        <v>2124</v>
+      </c>
+      <c r="B1196" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:2">
+      <c r="A1197" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B1197" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:2">
+      <c r="A1198" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B1198" t="s">
+        <v>2128</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1194"/>
+  <autoFilter ref="A1:B1198"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
